--- a/data/trans_orig/IQ3002_MoAR-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ3002_MoAR-Provincia-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Meses en la que empezaron a comer cereales con gluten</t>
+          <t>Meses en la que empezaron a comer cereales con gluten (tasa de respuesta: 55,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +677,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,8; 10,63</t>
+          <t>5,8; 10,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,65; 11,03</t>
+          <t>6,67; 11,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,77; 9,81</t>
+          <t>5,76; 9,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,4; 7,26</t>
+          <t>5,47; 7,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,37; 10,52</t>
+          <t>6,4; 10,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,63; 7,36</t>
+          <t>5,63; 7,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,9; 8,03</t>
+          <t>5,84; 7,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,06; 9,93</t>
+          <t>7,02; 10,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,89; 7,77</t>
+          <t>5,92; 7,89</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +787,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,74; 7,74</t>
+          <t>5,74; 7,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,37; 11,13</t>
+          <t>8,4; 11,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,83; 8,35</t>
+          <t>4,76; 8,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,43; 6,96</t>
+          <t>5,37; 7,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,03; 10,62</t>
+          <t>7,01; 10,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,08; 8,25</t>
+          <t>7,09; 8,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,88; 7,07</t>
+          <t>5,89; 7,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,24; 10,31</t>
+          <t>8,28; 10,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,02; 7,93</t>
+          <t>6,02; 7,95</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 6,18</t>
+          <t>3,39; 6,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,37; 9,23</t>
+          <t>7,35; 9,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 5,67</t>
+          <t>4,31; 5,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 6,75</t>
+          <t>4,14; 6,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,73; 8,88</t>
+          <t>6,64; 8,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,12; 7,0</t>
+          <t>5,13; 7,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,42; 6,33</t>
+          <t>4,55; 6,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,13; 8,61</t>
+          <t>7,18; 8,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,9; 6,28</t>
+          <t>4,92; 6,31</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,0; 7,36</t>
+          <t>5,91; 7,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,46; 8,25</t>
+          <t>5,58; 8,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,97; 9,45</t>
+          <t>6,93; 9,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,08; 8,64</t>
+          <t>6,05; 8,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,36; 10,6</t>
+          <t>7,41; 10,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,28; 8,69</t>
+          <t>6,28; 8,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,23; 7,92</t>
+          <t>6,18; 7,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,73; 8,9</t>
+          <t>6,74; 8,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,79; 8,45</t>
+          <t>6,8; 8,66</t>
         </is>
       </c>
     </row>
@@ -1122,49 +1122,49 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,13; 9,36</t>
+          <t>6,15; 9,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,61; 14,52</t>
+          <t>8,62; 14,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,51; 8,84</t>
+          <t>6,51; 9,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,87; 10,74</t>
+          <t>7,05; 10,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,3; 11,41</t>
+          <t>6,3; 11,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,52; 7,87</t>
+          <t>6,52; 7,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,9; 9,61</t>
+          <t>7,04; 9,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,95; 11,91</t>
+          <t>7,85; 11,95</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1227,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,77; 7,42</t>
+          <t>5,74; 7,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,25; 10,35</t>
+          <t>6,26; 10,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,39; 8,28</t>
+          <t>5,43; 8,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,23; 7,35</t>
+          <t>6,23; 7,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,67; 8,83</t>
+          <t>6,66; 8,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,24; 8,15</t>
+          <t>5,23; 7,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,17; 7,11</t>
+          <t>6,14; 7,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,79; 8,87</t>
+          <t>6,75; 8,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,63; 7,76</t>
+          <t>5,69; 7,7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,62; 10,98</t>
+          <t>6,56; 10,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,66; 8,5</t>
+          <t>6,77; 8,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,4; 9,02</t>
+          <t>6,35; 8,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,76; 8,44</t>
+          <t>6,75; 8,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,15; 8,77</t>
+          <t>7,2; 8,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,17; 8,22</t>
+          <t>6,17; 8,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,93; 8,99</t>
+          <t>6,99; 9,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,18; 8,38</t>
+          <t>7,13; 8,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,57; 8,15</t>
+          <t>6,52; 8,18</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1447,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,05; 8,85</t>
+          <t>7,05; 8,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,04; 9,93</t>
+          <t>6,94; 9,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,97; 7,82</t>
+          <t>6,03; 7,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,98; 8,16</t>
+          <t>5,86; 8,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,73; 7,61</t>
+          <t>5,7; 7,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,22; 8,69</t>
+          <t>6,05; 8,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,68; 8,16</t>
+          <t>6,68; 8,15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,6; 8,41</t>
+          <t>6,55; 8,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,27; 7,73</t>
+          <t>6,31; 7,87</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1557,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,6; 7,71</t>
+          <t>6,57; 7,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,54; 8,6</t>
+          <t>7,56; 8,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,65; 7,84</t>
+          <t>6,62; 7,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,45; 7,21</t>
+          <t>6,46; 7,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,24; 8,25</t>
+          <t>7,32; 8,25</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,5; 7,4</t>
+          <t>6,5; 7,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,63; 7,3</t>
+          <t>6,63; 7,25</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,54; 8,27</t>
+          <t>7,54; 8,25</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,71; 7,44</t>
+          <t>6,7; 7,44</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3002_MoAR-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ3002_MoAR-Provincia-trans_orig.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,8; 10,72</t>
+          <t>5,8; 10,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,67; 11,1</t>
+          <t>6,59; 10,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,76; 9,67</t>
+          <t>5,77; 9,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,47; 7,25</t>
+          <t>5,48; 7,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,4; 10,35</t>
+          <t>6,21; 10,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,63; 7,22</t>
+          <t>5,63; 7,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,84; 7,85</t>
+          <t>5,85; 7,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,02; 10,08</t>
+          <t>7,11; 10,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,92; 7,89</t>
+          <t>5,97; 7,96</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,74; 7,59</t>
+          <t>5,82; 7,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,4; 11,17</t>
+          <t>8,45; 11,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,76; 8,55</t>
+          <t>4,68; 8,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,37; 7,02</t>
+          <t>5,48; 6,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,01; 10,6</t>
+          <t>7,23; 10,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,09; 8,33</t>
+          <t>7,1; 8,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,89; 7,07</t>
+          <t>5,89; 7,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,28; 10,51</t>
+          <t>8,25; 10,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,02; 7,95</t>
+          <t>6,01; 8,03</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 6,17</t>
+          <t>3,33; 6,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,35; 9,26</t>
+          <t>7,28; 9,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,31; 5,66</t>
+          <t>4,31; 5,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,14; 6,75</t>
+          <t>4,15; 6,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,64; 8,84</t>
+          <t>6,64; 8,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,13; 7,18</t>
+          <t>5,12; 7,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,55; 6,28</t>
+          <t>4,6; 6,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,18; 8,61</t>
+          <t>7,14; 8,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,92; 6,31</t>
+          <t>4,91; 6,36</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,91; 7,31</t>
+          <t>5,89; 7,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,58; 8,28</t>
+          <t>5,42; 8,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,93; 9,34</t>
+          <t>6,92; 9,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,05; 8,44</t>
+          <t>6,12; 8,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,41; 10,43</t>
+          <t>7,41; 10,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,28; 8,48</t>
+          <t>6,29; 8,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,18; 7,81</t>
+          <t>6,2; 7,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,74; 8,89</t>
+          <t>6,77; 8,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,8; 8,66</t>
+          <t>6,82; 8,48</t>
         </is>
       </c>
     </row>
@@ -1122,42 +1122,42 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,15; 9,4</t>
+          <t>6,25; 9,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,62; 14,43</t>
+          <t>8,58; 14,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,51; 9,17</t>
+          <t>6,51; 8,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,05; 10,74</t>
+          <t>6,83; 10,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,3; 11,71</t>
+          <t>6,3; 11,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,52; 7,86</t>
+          <t>6,52; 7,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,04; 9,69</t>
+          <t>6,95; 9,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,85; 11,95</t>
+          <t>7,98; 11,91</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,74; 7,17</t>
+          <t>5,74; 7,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,26; 10,17</t>
+          <t>6,49; 10,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,43; 8,3</t>
+          <t>5,56; 8,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,23; 7,34</t>
+          <t>6,24; 7,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,66; 8,77</t>
+          <t>6,63; 8,7</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,23; 7,98</t>
+          <t>5,36; 8,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,14; 7,13</t>
+          <t>6,12; 7,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,75; 8,7</t>
+          <t>6,82; 8,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,69; 7,7</t>
+          <t>5,69; 7,63</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,56; 10,96</t>
+          <t>6,56; 10,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,77; 8,57</t>
+          <t>6,66; 8,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,35; 8,83</t>
+          <t>6,48; 8,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,75; 8,51</t>
+          <t>6,7; 8,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,2; 8,87</t>
+          <t>7,19; 8,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,17; 8,27</t>
+          <t>6,1; 8,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,99; 9,1</t>
+          <t>6,99; 9,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,13; 8,38</t>
+          <t>7,2; 8,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,52; 8,18</t>
+          <t>6,54; 8,25</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1447,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,05; 8,88</t>
+          <t>7,06; 8,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,94; 9,81</t>
+          <t>6,99; 9,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,03; 7,93</t>
+          <t>5,95; 7,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,86; 8,29</t>
+          <t>5,93; 8,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,7; 7,69</t>
+          <t>5,71; 7,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,05; 8,58</t>
+          <t>6,15; 8,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,68; 8,15</t>
+          <t>6,66; 8,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,55; 8,35</t>
+          <t>6,54; 8,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,31; 7,87</t>
+          <t>6,34; 7,92</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1557,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,57; 7,65</t>
+          <t>6,62; 7,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,56; 8,66</t>
+          <t>7,53; 8,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,62; 7,82</t>
+          <t>6,62; 7,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,46; 7,23</t>
+          <t>6,46; 7,3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,32; 8,25</t>
+          <t>7,29; 8,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,5; 7,42</t>
+          <t>6,53; 7,45</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,63; 7,25</t>
+          <t>6,62; 7,23</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,54; 8,25</t>
+          <t>7,53; 8,25</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,7; 7,44</t>
+          <t>6,7; 7,46</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3002_MoAR-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ3002_MoAR-Provincia-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,26</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8,32</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6,36</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>7,37</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>8,37</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>7,26</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,26</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,32</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,36</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,8; 10,6</t>
+          <t>5,4; 7,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,59; 10,87</t>
+          <t>6,37; 10,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,77; 9,8</t>
+          <t>5,63; 7,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,48; 7,24</t>
+          <t>5,8; 10,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,21; 10,38</t>
+          <t>6,65; 11,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,63; 7,28</t>
+          <t>5,77; 9,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,85; 7,85</t>
+          <t>5,9; 8,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,11; 10,1</t>
+          <t>7,06; 9,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,97; 7,96</t>
+          <t>5,89; 7,77</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,25</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8,89</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,54</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>6,71</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>9,42</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>6,43</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,25</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8,89</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,54</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,82; 7,63</t>
+          <t>5,43; 6,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,45; 11,18</t>
+          <t>7,03; 10,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,68; 8,42</t>
+          <t>7,08; 8,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,48; 6,95</t>
+          <t>5,74; 7,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,23; 10,66</t>
+          <t>8,37; 11,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,1; 8,3</t>
+          <t>4,83; 8,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,89; 7,14</t>
+          <t>5,88; 7,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,25; 10,36</t>
+          <t>8,24; 10,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,01; 8,03</t>
+          <t>6,02; 7,93</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,99</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,45</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5,82</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>5,42</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>8,06</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4,98</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,99</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,45</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,82</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 6,18</t>
+          <t>4,0; 6,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,28; 9,26</t>
+          <t>6,73; 8,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,31; 5,67</t>
+          <t>5,12; 7,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,15; 6,75</t>
+          <t>3,56; 6,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,64; 8,89</t>
+          <t>7,37; 9,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,12; 7,16</t>
+          <t>4,0; 5,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,6; 6,31</t>
+          <t>4,42; 6,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,14; 8,58</t>
+          <t>7,13; 8,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,91; 6,36</t>
+          <t>4,9; 6,28</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7,01</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8,79</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7,09</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>6,59</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>6,69</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>8,09</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,01</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,79</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,09</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,89; 7,28</t>
+          <t>6,08; 8,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 8,21</t>
+          <t>7,36; 10,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,92; 9,47</t>
+          <t>6,28; 8,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,12; 8,56</t>
+          <t>6,0; 7,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,41; 10,39</t>
+          <t>5,46; 8,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,29; 8,5</t>
+          <t>6,97; 9,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,2; 7,88</t>
+          <t>6,23; 7,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,77; 8,98</t>
+          <t>6,73; 8,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,82; 8,48</t>
+          <t>6,79; 8,45</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,5</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8,93</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>8,15</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>6,55</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>7,53</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>10,58</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7,5</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>8,93</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>8,15</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6,51; 8,84</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6,87; 10,74</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6,3; 11,41</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>6,14; 6,86</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>6,25; 9,43</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8,58; 14,51</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6,51; 8,83</t>
-        </is>
-      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,83; 10,87</t>
+          <t>6,13; 9,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,3; 11,95</t>
+          <t>8,61; 14,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,52; 7,96</t>
+          <t>6,52; 7,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,95; 9,66</t>
+          <t>6,9; 9,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,98; 11,91</t>
+          <t>7,95; 11,91</t>
         </is>
       </c>
     </row>
@@ -1174,32 +1174,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6,71</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7,29</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6,38</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>6,46</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>8,05</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>6,77</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6,71</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7,29</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6,38</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,74; 7,43</t>
+          <t>6,23; 7,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,49; 10,5</t>
+          <t>6,67; 8,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,36</t>
+          <t>5,24; 8,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,24; 7,35</t>
+          <t>5,77; 7,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,63; 8,7</t>
+          <t>6,25; 10,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,36; 8,18</t>
+          <t>5,39; 8,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,12; 7,12</t>
+          <t>6,17; 7,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,82; 8,79</t>
+          <t>6,79; 8,87</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,69; 7,63</t>
+          <t>5,63; 7,76</t>
         </is>
       </c>
     </row>
@@ -1284,32 +1284,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7,54</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7,91</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7,12</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>7,98</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>7,6</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>7,5</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7,54</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,91</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,12</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,56; 10,88</t>
+          <t>6,76; 8,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,66; 8,58</t>
+          <t>7,15; 8,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,48; 8,98</t>
+          <t>6,17; 8,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,7; 8,43</t>
+          <t>6,62; 10,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,19; 8,91</t>
+          <t>6,66; 8,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,1; 8,24</t>
+          <t>6,4; 9,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,99; 9,39</t>
+          <t>6,93; 8,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,2; 8,38</t>
+          <t>7,18; 8,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,54; 8,25</t>
+          <t>6,57; 8,15</t>
         </is>
       </c>
     </row>
@@ -1394,32 +1394,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>6,87</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6,52</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7,23</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>7,94</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>8,17</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>6,79</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6,87</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>6,52</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>7,23</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1447,47 +1447,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,06; 8,85</t>
+          <t>5,98; 8,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,99; 9,78</t>
+          <t>5,73; 7,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,95; 7,87</t>
+          <t>6,22; 8,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,93; 8,22</t>
+          <t>7,05; 8,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,71; 7,52</t>
+          <t>7,04; 9,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,15; 8,65</t>
+          <t>5,97; 7,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,66; 8,16</t>
+          <t>6,68; 8,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,54; 8,36</t>
+          <t>6,6; 8,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,34; 7,92</t>
+          <t>6,27; 7,73</t>
         </is>
       </c>
     </row>
@@ -1504,32 +1504,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>6,82</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7,75</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6,96</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>7,05</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>8,03</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>7,18</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>6,82</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>7,75</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>6,96</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1557,47 +1557,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,62; 7,62</t>
+          <t>6,45; 7,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,53; 8,6</t>
+          <t>7,24; 8,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,62; 7,78</t>
+          <t>6,5; 7,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,46; 7,3</t>
+          <t>6,6; 7,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,29; 8,23</t>
+          <t>7,54; 8,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,53; 7,45</t>
+          <t>6,65; 7,84</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,62; 7,23</t>
+          <t>6,63; 7,3</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,53; 8,25</t>
+          <t>7,54; 8,27</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,7; 7,46</t>
+          <t>6,71; 7,44</t>
         </is>
       </c>
     </row>
